--- a/doc/Borrador para bbdd.xlsx
+++ b/doc/Borrador para bbdd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xavier.carril/Desktop/Gent Gran BD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xavier.carril/Desktop/Gent Gran BD/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F62152-70D5-E143-9AD2-9387F08613A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32A37A9-F7B5-5D49-96D2-398FD7321C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17980" yWindow="-5120" windowWidth="18000" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>BAIXAS</t>
   </si>
   <si>
-    <t>OBERVACIONES</t>
-  </si>
-  <si>
     <t>24.02.2025</t>
   </si>
   <si>
@@ -376,6 +373,9 @@
   </si>
   <si>
     <t>35017964G</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
   </si>
 </sst>
 </file>
@@ -524,7 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -538,9 +538,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -557,9 +554,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -578,9 +572,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -597,14 +588,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -890,19 +893,19 @@
   <dimension ref="A1:Z49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14" style="8" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" style="8" customWidth="1"/>
-    <col min="5" max="6" width="19.1640625" style="11" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="30.1640625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.5" style="8" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" style="9"/>
-    <col min="13" max="13" width="28.6640625" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="10.83203125" style="8"/>
+    <col min="1" max="1" width="11.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="14" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" style="7" customWidth="1"/>
+    <col min="5" max="6" width="19.1640625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="31" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.5" style="7" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="8"/>
+    <col min="13" max="13" width="28.6640625" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.2">
@@ -930,10 +933,10 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -943,802 +946,802 @@
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+    </row>
+    <row r="2" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15">
+        <v>3748</v>
+      </c>
+      <c r="B2" s="27">
+        <v>8</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-    </row>
-    <row r="2" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17">
-        <v>3748</v>
-      </c>
-      <c r="B2" s="18">
+      <c r="D2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="29">
+        <v>655220494</v>
+      </c>
+      <c r="J2" s="15"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="20">
+        <v>3749</v>
+      </c>
+      <c r="B3" s="21">
         <v>8</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C3" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="30">
+        <v>615193554</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
+        <v>3750</v>
+      </c>
+      <c r="B4" s="21">
+        <v>8</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="30">
+        <v>659097137</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="20">
+        <v>3751</v>
+      </c>
+      <c r="B5" s="16">
+        <v>8</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="29">
+        <v>625729464</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="17"/>
+      <c r="M5" s="10"/>
+    </row>
+    <row r="6" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>3752</v>
+      </c>
+      <c r="B6" s="16">
+        <v>7</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="29">
+        <v>692453024</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="17"/>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20">
+        <v>3753</v>
+      </c>
+      <c r="B7" s="16">
+        <v>7</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="29">
+        <v>630551956</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="17"/>
+      <c r="M7" s="10"/>
+    </row>
+    <row r="8" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>3754</v>
+      </c>
+      <c r="B8" s="16">
+        <v>8</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="29">
+        <v>615129808</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="17"/>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20">
+        <v>3755</v>
+      </c>
+      <c r="B9" s="16">
+        <v>7</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="29">
+        <v>667454470</v>
+      </c>
+      <c r="J9" s="15"/>
+      <c r="K9" s="17"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <v>3756</v>
+      </c>
+      <c r="B10" s="16">
+        <v>7</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="29">
+        <v>660827198</v>
+      </c>
+      <c r="J10" s="15"/>
+      <c r="K10" s="19"/>
+    </row>
+    <row r="11" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20">
+        <v>3757</v>
+      </c>
+      <c r="B11" s="16">
+        <v>7</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="29">
+        <v>696188433</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="19"/>
+    </row>
+    <row r="12" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="15">
+        <v>3758</v>
+      </c>
+      <c r="B12" s="16">
+        <v>7</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="29">
+        <v>654912981</v>
+      </c>
+      <c r="J12" s="15"/>
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20">
+        <v>3759</v>
+      </c>
+      <c r="B13" s="16">
+        <v>7</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="29">
+        <v>627257683</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20">
+        <v>2912</v>
+      </c>
+      <c r="B14" s="21">
+        <v>1</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="30">
+        <v>640208343</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="17"/>
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
+        <v>1532</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="21">
-        <v>655220494</v>
-      </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="22"/>
-    </row>
-    <row r="3" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="23">
-        <v>3749</v>
-      </c>
-      <c r="B3" s="24">
+      <c r="E15" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="29"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="17"/>
+      <c r="M15" s="10"/>
+    </row>
+    <row r="16" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>3760</v>
+      </c>
+      <c r="B16" s="16">
         <v>8</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="28">
-        <v>615193554</v>
-      </c>
-      <c r="J3" s="29"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-    </row>
-    <row r="4" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="17">
-        <v>3750</v>
-      </c>
-      <c r="B4" s="24">
+      <c r="C16" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="29">
+        <v>606762889</v>
+      </c>
+      <c r="J16" s="15"/>
+      <c r="K16" s="17"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="15">
+        <v>3761</v>
+      </c>
+      <c r="B17" s="16">
         <v>8</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="28">
-        <v>659097137</v>
-      </c>
-      <c r="J4" s="29"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-    </row>
-    <row r="5" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23">
-        <v>3751</v>
-      </c>
-      <c r="B5" s="18">
+      <c r="C17" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" s="29">
+        <v>675768029</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="17"/>
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
+        <v>3762</v>
+      </c>
+      <c r="B18" s="16">
         <v>8</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="21">
-        <v>625729464</v>
-      </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="19"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="17">
-        <v>3752</v>
-      </c>
-      <c r="B6" s="18">
-        <v>7</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="C18" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="21">
-        <v>692453024</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="19"/>
-      <c r="M6" s="11"/>
-    </row>
-    <row r="7" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23">
-        <v>3753</v>
-      </c>
-      <c r="B7" s="18">
-        <v>7</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="21">
-        <v>630551956</v>
-      </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="19"/>
-      <c r="M7" s="11"/>
-    </row>
-    <row r="8" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17">
-        <v>3754</v>
-      </c>
-      <c r="B8" s="18">
+      <c r="G18" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="29">
+        <v>692427991</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="15">
+        <v>3763</v>
+      </c>
+      <c r="B19" s="16">
         <v>8</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="21">
-        <v>615129808</v>
-      </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="19"/>
-      <c r="M8" s="11"/>
-    </row>
-    <row r="9" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23">
-        <v>3755</v>
-      </c>
-      <c r="B9" s="18">
-        <v>7</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="21">
-        <v>667454470</v>
-      </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="19"/>
-      <c r="M9" s="11"/>
-    </row>
-    <row r="10" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17">
-        <v>3756</v>
-      </c>
-      <c r="B10" s="18">
-        <v>7</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="21">
-        <v>660827198</v>
-      </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="22"/>
-    </row>
-    <row r="11" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23">
-        <v>3757</v>
-      </c>
-      <c r="B11" s="18">
-        <v>7</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="21">
-        <v>696188433</v>
-      </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="22"/>
-    </row>
-    <row r="12" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="17">
-        <v>3758</v>
-      </c>
-      <c r="B12" s="18">
-        <v>7</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="21">
-        <v>654912981</v>
-      </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="22"/>
-    </row>
-    <row r="13" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23">
-        <v>3759</v>
-      </c>
-      <c r="B13" s="18">
-        <v>7</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="19" t="s">
+      <c r="C19" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="21">
-        <v>627257683</v>
-      </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="22"/>
-    </row>
-    <row r="14" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23">
-        <v>2912</v>
-      </c>
-      <c r="B14" s="24">
-        <v>1</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14" s="28">
-        <v>640208343</v>
-      </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="19"/>
-      <c r="M14" s="11"/>
-    </row>
-    <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17">
-        <v>1532</v>
-      </c>
-      <c r="B15" s="18" t="s">
+      <c r="F19" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="20" t="s">
+      <c r="G19" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="29">
+        <v>608590785</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="19"/>
+    </row>
+    <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="15">
+        <v>3764</v>
+      </c>
+      <c r="B20" s="16">
+        <v>8</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="19"/>
-      <c r="M15" s="11"/>
-    </row>
-    <row r="16" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="17">
-        <v>3760</v>
-      </c>
-      <c r="B16" s="18">
+      <c r="D20" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="29">
+        <v>665941524</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="19"/>
+    </row>
+    <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="15">
+        <v>3765</v>
+      </c>
+      <c r="B21" s="16">
         <v>8</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="21">
-        <v>606762889</v>
-      </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="19"/>
-      <c r="M16" s="11"/>
-    </row>
-    <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="17">
-        <v>3761</v>
-      </c>
-      <c r="B17" s="18">
+      <c r="C21" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" s="29">
+        <v>633267216</v>
+      </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="19"/>
+    </row>
+    <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="15">
+        <v>3766</v>
+      </c>
+      <c r="B22" s="16">
         <v>8</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="21">
-        <v>675768029</v>
-      </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="19"/>
-      <c r="M17" s="11"/>
-    </row>
-    <row r="18" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="17">
-        <v>3762</v>
-      </c>
-      <c r="B18" s="18">
+      <c r="C22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="29">
+        <v>680593009</v>
+      </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="19"/>
+    </row>
+    <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="15">
+        <v>3767</v>
+      </c>
+      <c r="B23" s="16">
         <v>8</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" s="21">
-        <v>692427991</v>
-      </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17">
-        <v>3763</v>
-      </c>
-      <c r="B19" s="18">
-        <v>8</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" s="21">
-        <v>608590785</v>
-      </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="22"/>
-    </row>
-    <row r="20" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
-        <v>3764</v>
-      </c>
-      <c r="B20" s="18">
-        <v>8</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" s="21">
-        <v>665941524</v>
-      </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="22"/>
-    </row>
-    <row r="21" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
-        <v>3765</v>
-      </c>
-      <c r="B21" s="18">
-        <v>8</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="I21" s="21">
-        <v>633267216</v>
-      </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="22"/>
-    </row>
-    <row r="22" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17">
-        <v>3766</v>
-      </c>
-      <c r="B22" s="18">
-        <v>8</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="17" t="s">
+      <c r="C23" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="H22" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="21">
-        <v>680593009</v>
-      </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="22"/>
-    </row>
-    <row r="23" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="17">
-        <v>3767</v>
-      </c>
-      <c r="B23" s="18">
-        <v>8</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="I23" s="21">
+      <c r="I23" s="29">
         <v>679410248</v>
       </c>
-      <c r="J23" s="17"/>
-      <c r="K23" s="22"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="19"/>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K24" s="13"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K25" s="13"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K26" s="13"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K27" s="13"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K28" s="13"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K29" s="13"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K30" s="13"/>
+      <c r="K30" s="11"/>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K31" s="13"/>
+      <c r="K31" s="11"/>
     </row>
     <row r="32" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K32" s="13"/>
+      <c r="K32" s="11"/>
     </row>
     <row r="33" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K33" s="13"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H34" s="15"/>
-      <c r="K34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K35" s="13"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K36" s="13"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K37" s="13"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K38" s="13"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K39" s="13"/>
+      <c r="K39" s="11"/>
     </row>
     <row r="40" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K40" s="13"/>
+      <c r="K40" s="11"/>
     </row>
     <row r="41" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K41" s="13"/>
-      <c r="M41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="M41" s="10"/>
     </row>
     <row r="42" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K42" s="13"/>
-      <c r="M42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="M42" s="10"/>
     </row>
     <row r="43" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K43" s="13"/>
-      <c r="M43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="M43" s="10"/>
     </row>
     <row r="44" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K44" s="13"/>
-      <c r="M44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="M44" s="10"/>
     </row>
     <row r="45" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K45" s="13"/>
-      <c r="M45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="M45" s="10"/>
     </row>
     <row r="46" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K46" s="13"/>
-      <c r="M46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="M46" s="10"/>
     </row>
     <row r="47" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K47" s="13"/>
-      <c r="M47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="M47" s="10"/>
     </row>
     <row r="48" spans="8:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K48" s="13"/>
-      <c r="M48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="M48" s="10"/>
     </row>
     <row r="49" spans="11:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K49" s="13"/>
-      <c r="M49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="M49" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
